--- a/Тест2/217.xlsx
+++ b/Тест2/217.xlsx
@@ -255,16 +255,16 @@
     <t xml:space="preserve">Begona mikroblar natijani buzmasligi uchun</t>
   </si>
   <si>
-    <t xml:space="preserve">Namunani ko'paytirish uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Namuna rangini o'zgartirish uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Namuna hajmini oshirish uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antibiotikni kuchaytirish uchun</t>
+    <t xml:space="preserve">Namunani ko'paytirib olish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namuna rangini o'zgartirib qo'yish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namuna hajmini oshirib yuborish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antibiotikni kuchaytirib yuborish uchun</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Begona mikroblar natijani buzmasligi uchun. Aseptika qoidalari qat'iy saqlanishi kerak, aks holda begona mikroblar natijani buzishi mumkin. Manba: Mavzu materiali (217.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
